--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_108.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_108.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72F4D6F0-02A7-4C89-9FF9-2E9637DDFBF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC8A7127-5EA9-4271-9456-0B6E5B03CBA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -777,13 +777,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S01aH10,S02aH11,S04aH12,S02aH13,S04aH05,S04aH08,S04aH04,S05aH10,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S02aH14,S03aH11,S04aH03,S05aH13,S05aH11,S01aH14,S04aH14,S05aH08,S06aH13,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S01aH09,S03aH04,S06aH14,S01aH03,S02aH10,S05aH03,S05aH06,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S01aH11,S04aH10,S06aH06,S06aH10,S03aH03</t>
+    <t>S01aH03,S02aH10,S05aH03,S05aH06,S01aH10,S02aH11,S04aH12,S01aH14,S04aH14,S05aH08,S06aH13,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S01aH09,S03aH04,S06aH14,S01aH11,S04aH10,S06aH06,S06aH10,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S04aH04,S05aH10,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S05aH11,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S02aH14,S03aH11,S04aH03,S05aH13,S02aH13,S04aH05,S04aH08</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH15,S04aH15,S02aH18,S03aH16,S04aH02,S06aH17,S03aH15,S03aH18,S02aH17,S05aH17,S01aH18,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S03aH02,S04aH18,S01aH16,S06aH01,S01aH02,S05aH01,S06aH15,S06aH16,S04aH17,S05aH15,S01aH01,S04aH01,S06aH02,S06aH18,S01aH15,S03aH01,S05aH16,S02aH02,S02aH16,S03aH17</t>
+    <t>S04aH17,S05aH15,S02aH18,S03aH16,S04aH02,S06aH17,S01aH16,S06aH01,S02aH02,S02aH16,S03aH17,S01aH02,S05aH01,S06aH15,S06aH16,S01aH15,S03aH01,S05aH16,S02aH15,S04aH15,S05aH17,S02aH17,S01aH01,S04aH01,S06aH02,S06aH18,S03aH02,S04aH18,S01aH18,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S03aH15,S03aH18</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH15,S04aH15,S02aH18,S03aH16,S04aH02,S06aH17,S03aH15,S03aH18,S02aH17,S05aH17,S01aH18,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S03aH02,S04aH18,S01aH16,S06aH01,S01aH02,S05aH01,S06aH15,S06aH16,S04aH17,S05aH15,S01aH01,S04aH01,S06aH02,S06aH18,S01aH15,S03aH01,S05aH16,S02aH02,S02aH16,S03aH17</v>
+        <v>S04aH17,S05aH15,S02aH18,S03aH16,S04aH02,S06aH17,S01aH16,S06aH01,S02aH02,S02aH16,S03aH17,S01aH02,S05aH01,S06aH15,S06aH16,S01aH15,S03aH01,S05aH16,S02aH15,S04aH15,S05aH17,S02aH17,S01aH01,S04aH01,S06aH02,S06aH18,S03aH02,S04aH18,S01aH18,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S03aH15,S03aH18</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S01aH10,S02aH11,S04aH12,S02aH13,S04aH05,S04aH08,S04aH04,S05aH10,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S02aH14,S03aH11,S04aH03,S05aH13,S05aH11,S01aH14,S04aH14,S05aH08,S06aH13,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S01aH09,S03aH04,S06aH14,S01aH03,S02aH10,S05aH03,S05aH06,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S01aH11,S04aH10,S06aH06,S06aH10,S03aH03</v>
+        <v>S01aH03,S02aH10,S05aH03,S05aH06,S01aH10,S02aH11,S04aH12,S01aH14,S04aH14,S05aH08,S06aH13,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S01aH09,S03aH04,S06aH14,S01aH11,S04aH10,S06aH06,S06aH10,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S04aH04,S05aH10,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S05aH11,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S02aH14,S03aH11,S04aH03,S05aH13,S02aH13,S04aH05,S04aH08</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1506,7 +1506,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4D4D5D0-A392-404E-9D04-475079D1CB9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3694A45-65D4-4FED-8A8C-855A2BF0FBEA}">
   <dimension ref="A9:G28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1714,7 +1714,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C579E6D1-0DC1-408A-9E9B-87CC0C9B7E60}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36F1EAD-C482-46A5-9D57-D3DDDF7A37C1}">
   <dimension ref="B9:J1630"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41288,7 +41288,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A00EB15A-131D-4101-A4D9-6490842C74F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68B2A914-41BB-49D6-9D91-FE93677FD221}">
   <dimension ref="B9:QF38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -62759,7 +62759,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74173E11-0E27-487F-9385-F3098AF2B098}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CE9BCD0-86C3-4BF7-AF22-A64AB6101F13}">
   <dimension ref="A9:S226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_108.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_108.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC8A7127-5EA9-4271-9456-0B6E5B03CBA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D845A99-23B3-430E-9A6A-2FA865BA5D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -777,13 +777,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH03,S02aH10,S05aH03,S05aH06,S01aH10,S02aH11,S04aH12,S01aH14,S04aH14,S05aH08,S06aH13,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S01aH09,S03aH04,S06aH14,S01aH11,S04aH10,S06aH06,S06aH10,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S04aH04,S05aH10,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S05aH11,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S02aH14,S03aH11,S04aH03,S05aH13,S02aH13,S04aH05,S04aH08</t>
+    <t>S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S01aH09,S03aH04,S06aH14,S03aH03,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S04aH04,S05aH10,S02aH14,S03aH11,S04aH03,S05aH13,S01aH14,S04aH14,S05aH08,S06aH13,S05aH11,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S01aH10,S02aH11,S04aH12,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S01aH11,S04aH10,S06aH06,S06aH10,S02aH13,S04aH05,S04aH08,S01aH03,S02aH10,S05aH03,S05aH06</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S04aH17,S05aH15,S02aH18,S03aH16,S04aH02,S06aH17,S01aH16,S06aH01,S02aH02,S02aH16,S03aH17,S01aH02,S05aH01,S06aH15,S06aH16,S01aH15,S03aH01,S05aH16,S02aH15,S04aH15,S05aH17,S02aH17,S01aH01,S04aH01,S06aH02,S06aH18,S03aH02,S04aH18,S01aH18,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S03aH15,S03aH18</t>
+    <t>S05aH17,S05aH01,S06aH15,S06aH16,S02aH02,S02aH16,S03aH17,S01aH01,S04aH01,S06aH02,S02aH17,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S01aH16,S06aH01,S03aH02,S04aH18,S02aH15,S04aH15,S01aH18,S06aH18,S02aH18,S03aH16,S04aH02,S06aH17,S01aH02,S01aH15,S03aH01,S05aH16,S03aH15,S03aH18,S04aH17,S05aH15</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S04aH17,S05aH15,S02aH18,S03aH16,S04aH02,S06aH17,S01aH16,S06aH01,S02aH02,S02aH16,S03aH17,S01aH02,S05aH01,S06aH15,S06aH16,S01aH15,S03aH01,S05aH16,S02aH15,S04aH15,S05aH17,S02aH17,S01aH01,S04aH01,S06aH02,S06aH18,S03aH02,S04aH18,S01aH18,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S03aH15,S03aH18</v>
+        <v>S05aH17,S05aH01,S06aH15,S06aH16,S02aH02,S02aH16,S03aH17,S01aH01,S04aH01,S06aH02,S02aH17,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S01aH16,S06aH01,S03aH02,S04aH18,S02aH15,S04aH15,S01aH18,S06aH18,S02aH18,S03aH16,S04aH02,S06aH17,S01aH02,S01aH15,S03aH01,S05aH16,S03aH15,S03aH18,S04aH17,S05aH15</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S01aH03,S02aH10,S05aH03,S05aH06,S01aH10,S02aH11,S04aH12,S01aH14,S04aH14,S05aH08,S06aH13,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S01aH09,S03aH04,S06aH14,S01aH11,S04aH10,S06aH06,S06aH10,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S04aH04,S05aH10,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S05aH11,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S02aH14,S03aH11,S04aH03,S05aH13,S02aH13,S04aH05,S04aH08</v>
+        <v>S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S01aH09,S03aH04,S06aH14,S03aH03,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S04aH04,S05aH10,S02aH14,S03aH11,S04aH03,S05aH13,S01aH14,S04aH14,S05aH08,S06aH13,S05aH11,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S01aH10,S02aH11,S04aH12,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S01aH11,S04aH10,S06aH06,S06aH10,S02aH13,S04aH05,S04aH08,S01aH03,S02aH10,S05aH03,S05aH06</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1506,7 +1506,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3694A45-65D4-4FED-8A8C-855A2BF0FBEA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5742F73B-4649-4409-9E1C-594D67E6F200}">
   <dimension ref="A9:G28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1714,7 +1714,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36F1EAD-C482-46A5-9D57-D3DDDF7A37C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76E3D215-743F-416F-9C1A-A96DA53086A9}">
   <dimension ref="B9:J1630"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41288,7 +41288,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68B2A914-41BB-49D6-9D91-FE93677FD221}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F9E29-2660-4FF3-8EF1-A9F9574ED44B}">
   <dimension ref="B9:QF38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -62759,7 +62759,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CE9BCD0-86C3-4BF7-AF22-A64AB6101F13}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBBDAD27-2182-4E71-9AEA-D7252155E200}">
   <dimension ref="A9:S226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_108.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_108.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D845A99-23B3-430E-9A6A-2FA865BA5D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0783B3C-CDA0-4EC3-9EFA-57B422B108E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -777,13 +777,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S01aH09,S03aH04,S06aH14,S03aH03,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S04aH04,S05aH10,S02aH14,S03aH11,S04aH03,S05aH13,S01aH14,S04aH14,S05aH08,S06aH13,S05aH11,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S01aH10,S02aH11,S04aH12,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S01aH11,S04aH10,S06aH06,S06aH10,S02aH13,S04aH05,S04aH08,S01aH03,S02aH10,S05aH03,S05aH06</t>
+    <t>S03aH03,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S01aH14,S04aH14,S05aH08,S06aH13,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S01aH10,S02aH11,S04aH12,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S05aH11,S04aH04,S05aH10,S01aH03,S02aH10,S05aH03,S05aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S01aH09,S03aH04,S06aH14,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S01aH11,S04aH10,S06aH06,S06aH10,S02aH14,S03aH11,S04aH03,S05aH13,S02aH13,S04aH05,S04aH08</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S05aH17,S05aH01,S06aH15,S06aH16,S02aH02,S02aH16,S03aH17,S01aH01,S04aH01,S06aH02,S02aH17,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S01aH16,S06aH01,S03aH02,S04aH18,S02aH15,S04aH15,S01aH18,S06aH18,S02aH18,S03aH16,S04aH02,S06aH17,S01aH02,S01aH15,S03aH01,S05aH16,S03aH15,S03aH18,S04aH17,S05aH15</t>
+    <t>S02aH02,S02aH16,S03aH17,S02aH15,S04aH15,S01aH16,S06aH01,S06aH18,S02aH18,S03aH16,S04aH02,S06aH17,S01aH01,S04aH01,S06aH02,S03aH02,S04aH18,S02aH17,S04aH17,S05aH15,S01aH02,S05aH17,S05aH01,S06aH15,S06aH16,S01aH18,S01aH15,S03aH01,S05aH16,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S03aH15,S03aH18</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S05aH17,S05aH01,S06aH15,S06aH16,S02aH02,S02aH16,S03aH17,S01aH01,S04aH01,S06aH02,S02aH17,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S01aH16,S06aH01,S03aH02,S04aH18,S02aH15,S04aH15,S01aH18,S06aH18,S02aH18,S03aH16,S04aH02,S06aH17,S01aH02,S01aH15,S03aH01,S05aH16,S03aH15,S03aH18,S04aH17,S05aH15</v>
+        <v>S02aH02,S02aH16,S03aH17,S02aH15,S04aH15,S01aH16,S06aH01,S06aH18,S02aH18,S03aH16,S04aH02,S06aH17,S01aH01,S04aH01,S06aH02,S03aH02,S04aH18,S02aH17,S04aH17,S05aH15,S01aH02,S05aH17,S05aH01,S06aH15,S06aH16,S01aH18,S01aH15,S03aH01,S05aH16,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S03aH15,S03aH18</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S01aH09,S03aH04,S06aH14,S03aH03,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S04aH04,S05aH10,S02aH14,S03aH11,S04aH03,S05aH13,S01aH14,S04aH14,S05aH08,S06aH13,S05aH11,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S01aH10,S02aH11,S04aH12,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S01aH11,S04aH10,S06aH06,S06aH10,S02aH13,S04aH05,S04aH08,S01aH03,S02aH10,S05aH03,S05aH06</v>
+        <v>S03aH03,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S01aH14,S04aH14,S05aH08,S06aH13,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S01aH10,S02aH11,S04aH12,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S05aH11,S04aH04,S05aH10,S01aH03,S02aH10,S05aH03,S05aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S01aH09,S03aH04,S06aH14,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S01aH11,S04aH10,S06aH06,S06aH10,S02aH14,S03aH11,S04aH03,S05aH13,S02aH13,S04aH05,S04aH08</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1506,7 +1506,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5742F73B-4649-4409-9E1C-594D67E6F200}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{654F793C-B97D-4270-9E10-1E7D4B3F4FAA}">
   <dimension ref="A9:G28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1714,7 +1714,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76E3D215-743F-416F-9C1A-A96DA53086A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32DD6E3E-C13D-4302-BC00-811EAC13A96E}">
   <dimension ref="B9:J1630"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41288,7 +41288,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31F9E29-2660-4FF3-8EF1-A9F9574ED44B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B040EBD-BF03-44C5-8F64-C4AF52938806}">
   <dimension ref="B9:QF38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -62759,7 +62759,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBBDAD27-2182-4E71-9AEA-D7252155E200}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C18972-BCD5-4D2D-84E4-90B88A97947F}">
   <dimension ref="A9:S226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_108.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_108.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0783B3C-CDA0-4EC3-9EFA-57B422B108E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9C3EC96-E917-46FC-A465-241B13B84F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -777,13 +777,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH03,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S01aH14,S04aH14,S05aH08,S06aH13,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S01aH10,S02aH11,S04aH12,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S05aH11,S04aH04,S05aH10,S01aH03,S02aH10,S05aH03,S05aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S01aH09,S03aH04,S06aH14,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S01aH11,S04aH10,S06aH06,S06aH10,S02aH14,S03aH11,S04aH03,S05aH13,S02aH13,S04aH05,S04aH08</t>
+    <t>S03aH03,S01aH14,S04aH14,S05aH08,S06aH13,S01aH11,S04aH10,S06aH06,S06aH10,S04aH04,S05aH10,S02aH13,S04aH05,S04aH08,S01aH10,S02aH11,S04aH12,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S02aH14,S03aH11,S04aH03,S05aH13,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S05aH11,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S01aH03,S02aH10,S05aH03,S05aH06,S01aH09,S03aH04,S06aH14,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH02,S02aH16,S03aH17,S02aH15,S04aH15,S01aH16,S06aH01,S06aH18,S02aH18,S03aH16,S04aH02,S06aH17,S01aH01,S04aH01,S06aH02,S03aH02,S04aH18,S02aH17,S04aH17,S05aH15,S01aH02,S05aH17,S05aH01,S06aH15,S06aH16,S01aH18,S01aH15,S03aH01,S05aH16,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S03aH15,S03aH18</t>
+    <t>S02aH02,S02aH16,S03aH17,S01aH16,S06aH01,S01aH15,S03aH01,S05aH16,S02aH17,S03aH15,S03aH18,S02aH18,S03aH16,S04aH02,S06aH17,S01aH01,S04aH01,S06aH02,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S01aH18,S03aH02,S04aH18,S06aH18,S02aH15,S04aH15,S05aH17,S04aH17,S05aH15,S05aH01,S06aH15,S06aH16,S01aH02</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH02,S02aH16,S03aH17,S02aH15,S04aH15,S01aH16,S06aH01,S06aH18,S02aH18,S03aH16,S04aH02,S06aH17,S01aH01,S04aH01,S06aH02,S03aH02,S04aH18,S02aH17,S04aH17,S05aH15,S01aH02,S05aH17,S05aH01,S06aH15,S06aH16,S01aH18,S01aH15,S03aH01,S05aH16,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S03aH15,S03aH18</v>
+        <v>S02aH02,S02aH16,S03aH17,S01aH16,S06aH01,S01aH15,S03aH01,S05aH16,S02aH17,S03aH15,S03aH18,S02aH18,S03aH16,S04aH02,S06aH17,S01aH01,S04aH01,S06aH02,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S01aH18,S03aH02,S04aH18,S06aH18,S02aH15,S04aH15,S05aH17,S04aH17,S05aH15,S05aH01,S06aH15,S06aH16,S01aH02</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S03aH03,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S01aH14,S04aH14,S05aH08,S06aH13,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S01aH10,S02aH11,S04aH12,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S05aH11,S04aH04,S05aH10,S01aH03,S02aH10,S05aH03,S05aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S01aH09,S03aH04,S06aH14,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S01aH11,S04aH10,S06aH06,S06aH10,S02aH14,S03aH11,S04aH03,S05aH13,S02aH13,S04aH05,S04aH08</v>
+        <v>S03aH03,S01aH14,S04aH14,S05aH08,S06aH13,S01aH11,S04aH10,S06aH06,S06aH10,S04aH04,S05aH10,S02aH13,S04aH05,S04aH08,S01aH10,S02aH11,S04aH12,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S02aH14,S03aH11,S04aH03,S05aH13,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S05aH11,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S01aH03,S02aH10,S05aH03,S05aH06,S01aH09,S03aH04,S06aH14,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1506,7 +1506,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{654F793C-B97D-4270-9E10-1E7D4B3F4FAA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A8E859-AF41-40C7-A25B-21D057F3E14D}">
   <dimension ref="A9:G28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1714,7 +1714,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32DD6E3E-C13D-4302-BC00-811EAC13A96E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F1BB2B5-B02E-4C16-B5A1-6BDEC4850EBB}">
   <dimension ref="B9:J1630"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41288,7 +41288,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B040EBD-BF03-44C5-8F64-C4AF52938806}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47266500-2EE9-4E25-86EE-97FFD3A93376}">
   <dimension ref="B9:QF38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -62759,7 +62759,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C18972-BCD5-4D2D-84E4-90B88A97947F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{592FBAAB-F554-4B76-9D65-BC6E8EDE6F0C}">
   <dimension ref="A9:S226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_108.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_TSParameters_ts_108.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE2E89B4-91ED-4E98-8ADF-4FF5E709D099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{43F209D8-02D5-4927-A78D-95E1221BFB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -846,13 +846,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S04aH04,S05aH10,S01aH11,S04aH10,S06aH06,S06aH10,S02aH14,S03aH11,S04aH03,S05aH13,S01aH10,S02aH11,S04aH12,S02aH13,S04aH05,S04aH08,S01aH09,S03aH04,S06aH14,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S01aH14,S04aH14,S05aH08,S06aH13,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S05aH11,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S01aH03,S02aH10,S05aH03,S05aH06,S03aH03</t>
+    <t>S03aH03,S01aH10,S02aH11,S04aH12,S01aH14,S04aH14,S05aH08,S06aH13,S02aH14,S03aH11,S04aH03,S05aH13,S01aH03,S02aH10,S05aH03,S05aH06,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S04aH04,S05aH10,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S05aH11,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S01aH09,S03aH04,S06aH14,S01aH11,S04aH10,S06aH06,S06aH10,S02aH13,S04aH05,S04aH08</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH17,S01aH15,S03aH01,S05aH16,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S02aH18,S03aH16,S04aH02,S06aH17,S03aH15,S03aH18,S05aH01,S06aH15,S06aH16,S01aH01,S04aH01,S06aH02,S01aH02,S01aH18,S01aH16,S06aH01,S06aH18,S03aH02,S04aH18,S02aH15,S04aH15,S05aH17,S04aH17,S05aH15,S02aH02,S02aH16,S03aH17</t>
+    <t>S02aH02,S02aH16,S03aH17,S02aH18,S03aH16,S04aH02,S06aH17,S01aH16,S06aH01,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S04aH17,S05aH15,S01aH01,S04aH01,S06aH02,S02aH15,S04aH15,S02aH17,S06aH18,S01aH18,S03aH02,S04aH18,S01aH02,S05aH17,S05aH01,S06aH15,S06aH16,S01aH15,S03aH01,S05aH16,S03aH15,S03aH18</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH17,S01aH15,S03aH01,S05aH16,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S02aH18,S03aH16,S04aH02,S06aH17,S03aH15,S03aH18,S05aH01,S06aH15,S06aH16,S01aH01,S04aH01,S06aH02,S01aH02,S01aH18,S01aH16,S06aH01,S06aH18,S03aH02,S04aH18,S02aH15,S04aH15,S05aH17,S04aH17,S05aH15,S02aH02,S02aH16,S03aH17</v>
+        <v>S02aH02,S02aH16,S03aH17,S02aH18,S03aH16,S04aH02,S06aH17,S01aH16,S06aH01,S01aH17,S02aH01,S04aH16,S05aH02,S05aH18,S04aH17,S05aH15,S01aH01,S04aH01,S06aH02,S02aH15,S04aH15,S02aH17,S06aH18,S01aH18,S03aH02,S04aH18,S01aH02,S05aH17,S05aH01,S06aH15,S06aH16,S01aH15,S03aH01,S05aH16,S03aH15,S03aH18</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S04aH04,S05aH10,S01aH11,S04aH10,S06aH06,S06aH10,S02aH14,S03aH11,S04aH03,S05aH13,S01aH10,S02aH11,S04aH12,S02aH13,S04aH05,S04aH08,S01aH09,S03aH04,S06aH14,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S01aH14,S04aH14,S05aH08,S06aH13,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S05aH11,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S01aH03,S02aH10,S05aH03,S05aH06,S03aH03</v>
+        <v>S03aH03,S01aH10,S02aH11,S04aH12,S01aH14,S04aH14,S05aH08,S06aH13,S02aH14,S03aH11,S04aH03,S05aH13,S01aH03,S02aH10,S05aH03,S05aH06,S01aH06,S01aH12,S02aH03,S05aH07,S06aH09,S06aH11,S02aH12,S04aH06,S04aH13,S05aH04,S06aH03,S04aH04,S05aH10,S01aH04,S01aH07,S01aH13,S02aH07,S02aH09,S03aH13,S04aH09,S04aH11,S05aH12,S02aH04,S02aH05,S03aH09,S03aH14,S05aH09,S05aH14,S06aH07,S05aH11,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH12,S06aH05,S02aH06,S03aH05,S03aH08,S03aH10,S04aH07,S05aH05,S06aH04,S06aH08,S06aH12,S01aH09,S03aH04,S06aH14,S01aH11,S04aH10,S06aH06,S06aH10,S02aH13,S04aH05,S04aH08</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1575,7 +1575,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A48725DF-6192-4EE8-BA4F-E7213C3C9E91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A246E7F-D4EA-4D25-995C-C3FBC31E171B}">
   <dimension ref="A9:G28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1783,7 +1783,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54E0D352-2D57-4216-A9BA-6DE42EB3D266}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1F1F91F-CDC6-4D31-AA14-EDD15BD133C2}">
   <dimension ref="B9:O1630"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -55629,7 +55629,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3A25761-D509-4876-B577-8A5A39DE5227}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D11467A9-78C4-420E-8779-7BBFF704D844}">
   <dimension ref="B9:QF49"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -85141,7 +85141,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB03852F-0D47-430F-AC9A-067FF509FB89}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4639B9A-D0D7-45B9-A922-49197A4A0431}">
   <dimension ref="A9:S226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
